--- a/grupos/2BEM - Estadisticos 20212.xlsx
+++ b/grupos/2BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -950,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -1104,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1181,7 +1181,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1258,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1341,7 +1341,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>-1</v>
@@ -1412,7 +1412,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1489,7 +1489,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -1626,7 +1626,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -1643,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1697,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1797,7 +1797,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1951,7 +1951,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2028,7 +2028,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>-1</v>
@@ -2082,7 +2082,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2111,7 +2111,7 @@
         <v>-1</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2182,7 +2182,7 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2413,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2467,7 +2467,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2496,7 +2496,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -2550,7 +2550,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -2567,7 +2567,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2621,7 +2621,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2644,7 +2644,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2798,7 +2798,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -2852,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -2875,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -2929,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -2952,7 +2952,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -3006,7 +3006,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3029,7 +3029,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -3083,7 +3083,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3106,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3160,7 +3160,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3183,7 +3183,7 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3237,7 +3237,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3266,7 +3266,7 @@
         <v>-1</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -3320,7 +3320,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>-1</v>
@@ -3337,7 +3337,7 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -3391,7 +3391,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3526,22 +3526,25 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>7.6</v>
+      </c>
       <c r="I4">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3590,22 +3593,22 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>84.38</v>
       </c>
       <c r="G6">
+        <v>15.63</v>
+      </c>
+      <c r="H6">
+        <v>8.9</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>9.6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3647,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3716,22 +3719,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920185</v>
+        <v>21330051920186</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3748,10 +3751,10 @@
         <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3768,30 +3771,30 @@
         <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920186</v>
+        <v>21330051920187</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3808,64 +3811,64 @@
         <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920187</v>
+        <v>21330051920188</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920187</v>
+        <v>21330051920188</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920188</v>
+        <v>21330051920189</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -3876,16 +3879,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920188</v>
+        <v>21330051920189</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -3896,116 +3899,116 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920188</v>
+        <v>21330051920190</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920189</v>
+        <v>21330051920190</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920189</v>
+        <v>21330051920190</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920189</v>
+        <v>21330051920191</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920190</v>
+        <v>21330051920191</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920190</v>
+        <v>21330051920192</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -4016,16 +4019,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920190</v>
+        <v>21330051920192</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -4036,496 +4039,496 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920190</v>
+        <v>21330051920193</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920191</v>
+        <v>21330051920193</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920191</v>
+        <v>19330061430023</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920191</v>
+        <v>19330061430023</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920192</v>
+        <v>19330061430023</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920192</v>
+        <v>19330061430023</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920192</v>
+        <v>21330051920194</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920193</v>
+        <v>21330051920194</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920193</v>
+        <v>21330051920195</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920193</v>
+        <v>21330051920195</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330061430023</v>
+        <v>21330051920195</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330061430023</v>
+        <v>21330051920196</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330061430023</v>
+        <v>21330051920196</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330061430023</v>
+        <v>21330051920197</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920194</v>
+        <v>21330051920197</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920194</v>
+        <v>21330051920197</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920194</v>
+        <v>21330051920386</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920195</v>
+        <v>21330051920386</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920195</v>
+        <v>21330051920198</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920195</v>
+        <v>21330051920198</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920196</v>
+        <v>21330051920198</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920196</v>
+        <v>21330051920198</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920196</v>
+        <v>21330051920199</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920197</v>
+        <v>21330051920199</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920197</v>
+        <v>21330051920200</v>
       </c>
       <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
         <v>73</v>
       </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
       <c r="D44" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -4536,16 +4539,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920197</v>
+        <v>21330051920200</v>
       </c>
       <c r="B45" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" t="s">
         <v>73</v>
       </c>
-      <c r="C45" t="s">
-        <v>102</v>
-      </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -4556,16 +4559,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920197</v>
+        <v>21330051920200</v>
       </c>
       <c r="B46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" t="s">
         <v>73</v>
       </c>
-      <c r="C46" t="s">
-        <v>102</v>
-      </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
         <v>6</v>
@@ -4576,16 +4579,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920386</v>
+        <v>21330051920201</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -4596,16 +4599,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920386</v>
+        <v>21330051920201</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -4616,16 +4619,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920386</v>
+        <v>21330051920201</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E49" t="s">
         <v>6</v>
@@ -4636,116 +4639,116 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920198</v>
+        <v>21330051920202</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920198</v>
+        <v>21330051920202</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D51" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920198</v>
+        <v>21330051920203</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920198</v>
+        <v>21330051920203</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920198</v>
+        <v>21330051920203</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D54" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920199</v>
+        <v>21330051920204</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D55" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -4756,16 +4759,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920199</v>
+        <v>21330051920204</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D56" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -4776,96 +4779,96 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920199</v>
+        <v>21330051920205</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D57" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920200</v>
+        <v>21330051920205</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="D58" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920200</v>
+        <v>21330051920206</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D59" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920200</v>
+        <v>21330051920206</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D60" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21330051920201</v>
+        <v>21330051920207</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -4876,16 +4879,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051920201</v>
+        <v>21330051920207</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
@@ -4896,16 +4899,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051920201</v>
+        <v>21330051920207</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E63" t="s">
         <v>6</v>
@@ -4916,16 +4919,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051920202</v>
+        <v>21330051920208</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -4936,16 +4939,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>21330051920202</v>
+        <v>21330051920208</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E65" t="s">
         <v>7</v>
@@ -4956,56 +4959,56 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>21330051920202</v>
+        <v>21330051920209</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E66" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920203</v>
+        <v>21330051920209</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D67" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F67" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920203</v>
+        <v>21330051920210</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -5016,16 +5019,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920203</v>
+        <v>21330051920210</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
         <v>7</v>
@@ -5036,96 +5039,96 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920203</v>
+        <v>21330051920211</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>21330051920204</v>
+        <v>21330051920211</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F71" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>21330051920204</v>
+        <v>21330051920212</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D72" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>21330051920204</v>
+        <v>21330051920212</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C73" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E73" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>21330051920205</v>
+        <v>21330051920213</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C74" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -5136,16 +5139,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>21330051920205</v>
+        <v>21330051920213</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E75" t="s">
         <v>7</v>
@@ -5156,16 +5159,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>21330051920205</v>
+        <v>21330051920213</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C76" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E76" t="s">
         <v>6</v>
@@ -5176,582 +5179,62 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>21330051920206</v>
+        <v>21330051920213</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E77" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F77" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>21330051920206</v>
+        <v>21330051920214</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C78" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D78" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>21330051920206</v>
+        <v>21330051920214</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E79" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920207</v>
-      </c>
-      <c r="B80" t="s">
-        <v>84</v>
-      </c>
-      <c r="C80" t="s">
-        <v>87</v>
-      </c>
-      <c r="D80" t="s">
-        <v>140</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920207</v>
-      </c>
-      <c r="B81" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" t="s">
-        <v>87</v>
-      </c>
-      <c r="D81" t="s">
-        <v>140</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920207</v>
-      </c>
-      <c r="B82" t="s">
-        <v>84</v>
-      </c>
-      <c r="C82" t="s">
-        <v>87</v>
-      </c>
-      <c r="D82" t="s">
-        <v>140</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920208</v>
-      </c>
-      <c r="B83" t="s">
-        <v>85</v>
-      </c>
-      <c r="C83" t="s">
-        <v>95</v>
-      </c>
-      <c r="D83" t="s">
-        <v>141</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920208</v>
-      </c>
-      <c r="B84" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" t="s">
-        <v>95</v>
-      </c>
-      <c r="D84" t="s">
-        <v>141</v>
-      </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920208</v>
-      </c>
-      <c r="B85" t="s">
-        <v>85</v>
-      </c>
-      <c r="C85" t="s">
-        <v>95</v>
-      </c>
-      <c r="D85" t="s">
-        <v>141</v>
-      </c>
-      <c r="E85" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920209</v>
-      </c>
-      <c r="B86" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" t="s">
-        <v>111</v>
-      </c>
-      <c r="D86" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920209</v>
-      </c>
-      <c r="B87" t="s">
-        <v>86</v>
-      </c>
-      <c r="C87" t="s">
-        <v>111</v>
-      </c>
-      <c r="D87" t="s">
-        <v>142</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920209</v>
-      </c>
-      <c r="B88" t="s">
-        <v>86</v>
-      </c>
-      <c r="C88" t="s">
-        <v>111</v>
-      </c>
-      <c r="D88" t="s">
-        <v>142</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920210</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>112</v>
-      </c>
-      <c r="D89" t="s">
-        <v>143</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920210</v>
-      </c>
-      <c r="B90" t="s">
-        <v>87</v>
-      </c>
-      <c r="C90" t="s">
-        <v>112</v>
-      </c>
-      <c r="D90" t="s">
-        <v>143</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920210</v>
-      </c>
-      <c r="B91" t="s">
-        <v>87</v>
-      </c>
-      <c r="C91" t="s">
-        <v>112</v>
-      </c>
-      <c r="D91" t="s">
-        <v>143</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920211</v>
-      </c>
-      <c r="B92" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" t="s">
-        <v>97</v>
-      </c>
-      <c r="D92" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920211</v>
-      </c>
-      <c r="B93" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" t="s">
-        <v>97</v>
-      </c>
-      <c r="D93" t="s">
-        <v>144</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920211</v>
-      </c>
-      <c r="B94" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" t="s">
-        <v>97</v>
-      </c>
-      <c r="D94" t="s">
-        <v>144</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920212</v>
-      </c>
-      <c r="B95" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" t="s">
-        <v>113</v>
-      </c>
-      <c r="D95" t="s">
-        <v>145</v>
-      </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920212</v>
-      </c>
-      <c r="B96" t="s">
-        <v>89</v>
-      </c>
-      <c r="C96" t="s">
-        <v>113</v>
-      </c>
-      <c r="D96" t="s">
-        <v>145</v>
-      </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920212</v>
-      </c>
-      <c r="B97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C97" t="s">
-        <v>113</v>
-      </c>
-      <c r="D97" t="s">
-        <v>145</v>
-      </c>
-      <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920213</v>
-      </c>
-      <c r="B98" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" t="s">
-        <v>114</v>
-      </c>
-      <c r="D98" t="s">
-        <v>146</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920213</v>
-      </c>
-      <c r="B99" t="s">
-        <v>90</v>
-      </c>
-      <c r="C99" t="s">
-        <v>114</v>
-      </c>
-      <c r="D99" t="s">
-        <v>146</v>
-      </c>
-      <c r="E99" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920213</v>
-      </c>
-      <c r="B100" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" t="s">
-        <v>114</v>
-      </c>
-      <c r="D100" t="s">
-        <v>146</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920213</v>
-      </c>
-      <c r="B101" t="s">
-        <v>90</v>
-      </c>
-      <c r="C101" t="s">
-        <v>114</v>
-      </c>
-      <c r="D101" t="s">
-        <v>146</v>
-      </c>
-      <c r="E101" t="s">
-        <v>6</v>
-      </c>
-      <c r="F101" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920213</v>
-      </c>
-      <c r="B102" t="s">
-        <v>90</v>
-      </c>
-      <c r="C102" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" t="s">
-        <v>146</v>
-      </c>
-      <c r="E102" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920214</v>
-      </c>
-      <c r="B103" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" t="s">
-        <v>115</v>
-      </c>
-      <c r="D103" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" t="s">
-        <v>9</v>
-      </c>
-      <c r="F103" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920214</v>
-      </c>
-      <c r="B104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" t="s">
-        <v>115</v>
-      </c>
-      <c r="D104" t="s">
-        <v>147</v>
-      </c>
-      <c r="E104" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920214</v>
-      </c>
-      <c r="B105" t="s">
-        <v>91</v>
-      </c>
-      <c r="C105" t="s">
-        <v>115</v>
-      </c>
-      <c r="D105" t="s">
-        <v>147</v>
-      </c>
-      <c r="E105" t="s">
-        <v>6</v>
-      </c>
-      <c r="F105" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -5787,50 +5270,50 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920198</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920213</v>
+        <v>21330051920198</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920190</v>
+        <v>21330051920213</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5838,67 +5321,67 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920186</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920197</v>
+        <v>21330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920203</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920185</v>
+        <v>21330051920197</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5906,16 +5389,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920186</v>
+        <v>21330051920200</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5923,16 +5406,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920187</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -5940,16 +5423,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920188</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -5957,16 +5440,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920189</v>
+        <v>21330051920207</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -5974,257 +5457,257 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920191</v>
+        <v>21330051920185</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920192</v>
+        <v>21330051920187</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920193</v>
+        <v>21330051920188</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920194</v>
+        <v>21330051920189</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920195</v>
+        <v>21330051920191</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920196</v>
+        <v>21330051920192</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920386</v>
+        <v>21330051920193</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920199</v>
+        <v>21330051920194</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920200</v>
+        <v>21330051920196</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920201</v>
+        <v>21330051920386</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920202</v>
+        <v>21330051920199</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920204</v>
+        <v>21330051920202</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920205</v>
+        <v>21330051920204</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920206</v>
+        <v>21330051920205</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920207</v>
+        <v>21330051920206</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6241,7 +5724,7 @@
         <v>141</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6258,7 +5741,7 @@
         <v>142</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6275,7 +5758,7 @@
         <v>143</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6292,7 +5775,7 @@
         <v>144</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6309,7 +5792,7 @@
         <v>145</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6326,7 +5809,7 @@
         <v>147</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6336,7 +5819,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6366,6 +5849,788 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920187</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920187</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920188</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920188</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920189</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920191</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920191</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920194</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920194</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920196</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920386</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920386</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920199</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920199</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920204</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920205</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920205</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920206</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920206</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920208</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920208</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920210</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920210</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920211</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920211</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920212</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920212</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="s">
+        <v>145</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>147</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2BEM - Estadisticos 20212.xlsx
+++ b/grupos/2BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -179,24 +179,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Aurioles Maldonado Luis Gustavo</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Aurioles Maldonado Luis Gustavo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,57 +212,123 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
     <t>BERNABE</t>
   </si>
   <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>CERON</t>
   </si>
   <si>
     <t>CHULIN</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>ELVIRA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>MEZA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>QUIJANO</t>
   </si>
   <si>
@@ -272,27 +338,15 @@
     <t>ROSALIANO</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -308,42 +362,24 @@
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -362,18 +398,12 @@
     <t>PIEDRAS</t>
   </si>
   <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>CUICAHUA</t>
   </si>
   <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
     <t>NEIL</t>
   </si>
   <si>
@@ -383,9 +413,6 @@
     <t>ANGEL ALDAIR</t>
   </si>
   <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
     <t>ITZEL</t>
   </si>
   <si>
@@ -395,42 +422,21 @@
     <t>JASIEL</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
     <t>JULIO</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>CELSO ALEJANDRO</t>
   </si>
   <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
     <t>GREGORIO</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
     <t>WENCESLAO</t>
   </si>
   <si>
-    <t>ADAHIR</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
     <t>JOSE ALEJANDRO</t>
   </si>
   <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
     <t>JUAN PABLO</t>
   </si>
   <si>
@@ -440,9 +446,6 @@
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
     <t>ZURIEL ELIHU</t>
   </si>
   <si>
@@ -456,9 +459,6 @@
   </si>
   <si>
     <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
   <si>
     <t>DARINKA</t>
@@ -953,13 +953,13 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -1007,13 +1007,13 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1030,13 +1030,13 @@
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -1084,13 +1084,13 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1107,13 +1107,13 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1161,13 +1161,13 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1184,13 +1184,13 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1238,13 +1238,13 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1261,13 +1261,13 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1315,13 +1315,13 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1344,7 +1344,7 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>7</v>
@@ -1398,7 +1398,7 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1415,13 +1415,13 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -1469,13 +1469,13 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1492,13 +1492,13 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1546,13 +1546,13 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1569,13 +1569,13 @@
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -1623,13 +1623,13 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1646,13 +1646,13 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1700,13 +1700,13 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1723,13 +1723,13 @@
         <v>-1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1777,13 +1777,13 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1800,13 +1800,13 @@
         <v>8</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -1854,13 +1854,13 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1883,7 +1883,7 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1954,13 +1954,13 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -2008,13 +2008,13 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2031,13 +2031,13 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -2085,13 +2085,13 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2185,13 +2185,13 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2239,13 +2239,13 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2262,13 +2262,13 @@
         <v>-1</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>7</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2316,13 +2316,13 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2339,13 +2339,13 @@
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>10</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2393,13 +2393,13 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2416,13 +2416,13 @@
         <v>9</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2470,13 +2470,13 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2499,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2570,13 +2570,13 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>7</v>
@@ -2624,13 +2624,13 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2647,13 +2647,13 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -2701,13 +2701,13 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2724,13 +2724,13 @@
         <v>-1</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>9</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G27">
         <v>7</v>
@@ -2778,13 +2778,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2801,13 +2801,13 @@
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -2855,13 +2855,13 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2878,13 +2878,13 @@
         <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>10</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -2932,13 +2932,13 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2955,13 +2955,13 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3009,13 +3009,13 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -3032,13 +3032,13 @@
         <v>8</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -3086,13 +3086,13 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3109,13 +3109,13 @@
         <v>8</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>6</v>
@@ -3163,13 +3163,13 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3186,13 +3186,13 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>6</v>
@@ -3240,13 +3240,13 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3340,13 +3340,13 @@
         <v>8</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3394,13 +3394,13 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>10</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3468,27 +3468,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.6</v>
+      </c>
       <c r="I2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3497,27 +3500,30 @@
         <v>32</v>
       </c>
       <c r="D3">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>65.63</v>
+      </c>
+      <c r="G3">
+        <v>34.38</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3526,30 +3532,30 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>84.38</v>
+      </c>
+      <c r="G4">
+        <v>15.63</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>65.63</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.6</v>
-      </c>
-      <c r="I4">
-        <v>11</v>
-      </c>
-      <c r="J4">
-        <v>34.38</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3558,30 +3564,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>65.63</v>
+        <v>84.38</v>
       </c>
       <c r="G5">
-        <v>34.38</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3590,30 +3596,30 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="G6">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3622,25 +3628,25 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>
@@ -3650,7 +3656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,19 +3685,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920185</v>
+        <v>21330051920186</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -3699,39 +3705,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920185</v>
+        <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920186</v>
+        <v>21330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
@@ -3739,99 +3745,99 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920186</v>
+        <v>19330061430023</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920186</v>
+        <v>19330061430023</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920187</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920187</v>
+        <v>21330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920188</v>
+        <v>21330051920197</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -3839,179 +3845,179 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920188</v>
+        <v>21330051920198</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920189</v>
+        <v>21330051920198</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920189</v>
+        <v>21330051920198</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920190</v>
+        <v>21330051920198</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920190</v>
+        <v>21330051920200</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920190</v>
+        <v>21330051920201</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920191</v>
+        <v>21330051920203</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920191</v>
+        <v>21330051920203</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920192</v>
+        <v>21330051920207</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
@@ -4019,1222 +4025,82 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920192</v>
+        <v>21330051920213</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
         <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920193</v>
+        <v>21330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920193</v>
+        <v>21330051920213</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330061430023</v>
+        <v>21330051920213</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330061430023</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330061430023</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330061430023</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920194</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920194</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920195</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920195</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920195</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" t="s">
-        <v>127</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920196</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920196</v>
-      </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920197</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920197</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920197</v>
-      </c>
-      <c r="B35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920386</v>
-      </c>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920386</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920198</v>
-      </c>
-      <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920198</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" t="s">
-        <v>131</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920198</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920198</v>
-      </c>
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920199</v>
-      </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920199</v>
-      </c>
-      <c r="B43" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920200</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>73</v>
-      </c>
-      <c r="D44" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920200</v>
-      </c>
-      <c r="B45" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" t="s">
-        <v>133</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920200</v>
-      </c>
-      <c r="B46" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920201</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920201</v>
-      </c>
-      <c r="B48" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920201</v>
-      </c>
-      <c r="B49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920202</v>
-      </c>
-      <c r="B50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920202</v>
-      </c>
-      <c r="B51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920203</v>
-      </c>
-      <c r="B52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920203</v>
-      </c>
-      <c r="B53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920203</v>
-      </c>
-      <c r="B54" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920204</v>
-      </c>
-      <c r="B55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920204</v>
-      </c>
-      <c r="B56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920205</v>
-      </c>
-      <c r="B57" t="s">
-        <v>82</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" t="s">
-        <v>138</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920205</v>
-      </c>
-      <c r="B58" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920206</v>
-      </c>
-      <c r="B59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C59" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920206</v>
-      </c>
-      <c r="B60" t="s">
-        <v>83</v>
-      </c>
-      <c r="C60" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" t="s">
-        <v>139</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920207</v>
-      </c>
-      <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="s">
-        <v>87</v>
-      </c>
-      <c r="D61" t="s">
-        <v>140</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920207</v>
-      </c>
-      <c r="B62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" t="s">
-        <v>87</v>
-      </c>
-      <c r="D62" t="s">
-        <v>140</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920207</v>
-      </c>
-      <c r="B63" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" t="s">
-        <v>87</v>
-      </c>
-      <c r="D63" t="s">
-        <v>140</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920208</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" t="s">
-        <v>141</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920208</v>
-      </c>
-      <c r="B65" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65" t="s">
-        <v>95</v>
-      </c>
-      <c r="D65" t="s">
-        <v>141</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920209</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>111</v>
-      </c>
-      <c r="D66" t="s">
-        <v>142</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920209</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>111</v>
-      </c>
-      <c r="D67" t="s">
-        <v>142</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920210</v>
-      </c>
-      <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" t="s">
-        <v>143</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920210</v>
-      </c>
-      <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" t="s">
-        <v>143</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920211</v>
-      </c>
-      <c r="B70" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" t="s">
-        <v>144</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920211</v>
-      </c>
-      <c r="B71" t="s">
-        <v>88</v>
-      </c>
-      <c r="C71" t="s">
-        <v>97</v>
-      </c>
-      <c r="D71" t="s">
-        <v>144</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920212</v>
-      </c>
-      <c r="B72" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" t="s">
-        <v>113</v>
-      </c>
-      <c r="D72" t="s">
-        <v>145</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920212</v>
-      </c>
-      <c r="B73" t="s">
-        <v>89</v>
-      </c>
-      <c r="C73" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" t="s">
-        <v>145</v>
-      </c>
-      <c r="E73" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920213</v>
-      </c>
-      <c r="B74" t="s">
-        <v>90</v>
-      </c>
-      <c r="C74" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
-        <v>146</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920213</v>
-      </c>
-      <c r="B75" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
-        <v>146</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920213</v>
-      </c>
-      <c r="B76" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" t="s">
-        <v>146</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920213</v>
-      </c>
-      <c r="B77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77" t="s">
-        <v>114</v>
-      </c>
-      <c r="D77" t="s">
-        <v>146</v>
-      </c>
-      <c r="E77" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920214</v>
-      </c>
-      <c r="B78" t="s">
-        <v>91</v>
-      </c>
-      <c r="C78" t="s">
-        <v>115</v>
-      </c>
-      <c r="D78" t="s">
-        <v>147</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920214</v>
-      </c>
-      <c r="B79" t="s">
-        <v>91</v>
-      </c>
-      <c r="C79" t="s">
-        <v>115</v>
-      </c>
-      <c r="D79" t="s">
-        <v>147</v>
-      </c>
-      <c r="E79" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -5270,16 +4136,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330061430023</v>
+        <v>21330051920198</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -5287,16 +4153,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920198</v>
+        <v>21330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5304,138 +4170,138 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920213</v>
+        <v>21330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920186</v>
+        <v>19330061430023</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920190</v>
+        <v>21330051920195</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920195</v>
+        <v>21330051920203</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920197</v>
+        <v>21330051920186</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920200</v>
+        <v>21330051920197</v>
       </c>
       <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920201</v>
+        <v>21330051920200</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920203</v>
+        <v>21330051920201</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5443,16 +4309,16 @@
         <v>21330051920207</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5463,13 +4329,13 @@
         <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5477,16 +4343,16 @@
         <v>21330051920187</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5494,16 +4360,16 @@
         <v>21330051920188</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5511,16 +4377,16 @@
         <v>21330051920189</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5528,16 +4394,16 @@
         <v>21330051920191</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5545,16 +4411,16 @@
         <v>21330051920192</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5562,16 +4428,16 @@
         <v>21330051920193</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5579,16 +4445,16 @@
         <v>21330051920194</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5596,16 +4462,16 @@
         <v>21330051920196</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5613,16 +4479,16 @@
         <v>21330051920386</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5630,16 +4496,16 @@
         <v>21330051920199</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5647,16 +4513,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5664,16 +4530,16 @@
         <v>21330051920204</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5681,16 +4547,16 @@
         <v>21330051920205</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5698,16 +4564,16 @@
         <v>21330051920206</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5715,16 +4581,16 @@
         <v>21330051920208</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5732,16 +4598,16 @@
         <v>21330051920209</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5749,16 +4615,16 @@
         <v>21330051920210</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5766,16 +4632,16 @@
         <v>21330051920211</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5783,16 +4649,16 @@
         <v>21330051920212</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5800,16 +4666,16 @@
         <v>21330051920214</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5819,7 +4685,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5851,22 +4717,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920185</v>
+        <v>21330051920197</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5874,45 +4740,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920185</v>
+        <v>21330051920197</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920187</v>
+        <v>21330051920200</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5920,45 +4786,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920187</v>
+        <v>21330051920200</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920188</v>
+        <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5966,45 +4832,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920188</v>
+        <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920189</v>
+        <v>21330051920186</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6012,91 +4878,91 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920189</v>
+        <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920191</v>
+        <v>21330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920191</v>
+        <v>21330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920194</v>
+        <v>21330051920207</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -6104,531 +4970,25 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920194</v>
+        <v>21330051920209</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920196</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920196</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920386</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920386</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920199</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920199</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920204</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920204</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920205</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920205</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920206</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920206</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920208</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920208</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920210</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920210</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920211</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920211</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920212</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920212</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920214</v>
-      </c>
-      <c r="B34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920214</v>
-      </c>
-      <c r="B35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2BEM - Estadisticos 20212.xlsx
+++ b/grupos/2BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -188,13 +188,13 @@
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>NC</t>
@@ -965,16 +965,16 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1007,10 +1007,10 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1042,13 +1042,13 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1119,16 +1119,16 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1196,13 +1196,13 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1273,13 +1273,13 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1309,7 +1309,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1338,7 +1338,7 @@
         <v>-1</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1350,13 +1350,13 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1386,13 +1386,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1427,13 +1427,13 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1504,16 +1504,16 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1581,13 +1581,13 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1623,7 +1623,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1658,16 +1658,16 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1717,7 +1717,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>-1</v>
@@ -1735,13 +1735,13 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1812,16 +1812,16 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1877,7 +1877,7 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>7</v>
@@ -1889,13 +1889,13 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1966,16 +1966,16 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2043,13 +2043,13 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2085,7 +2085,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2102,13 +2102,13 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2120,13 +2120,13 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2156,13 +2156,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2197,16 +2197,16 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2274,13 +2274,13 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2351,13 +2351,13 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2428,13 +2428,13 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2493,7 +2493,7 @@
         <v>-1</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2505,13 +2505,13 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2582,16 +2582,16 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2659,16 +2659,16 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2813,16 +2813,16 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2855,7 +2855,7 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2890,16 +2890,16 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2967,13 +2967,13 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3044,16 +3044,16 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3121,16 +3121,16 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3198,13 +3198,13 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3234,13 +3234,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>7</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3257,13 +3257,13 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3275,13 +3275,13 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3311,13 +3311,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3352,16 +3352,16 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3388,7 +3388,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3397,7 +3397,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3544,7 +3544,7 @@
         <v>15.63</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3564,30 +3564,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>84.38</v>
+        <v>93.75</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>15.63</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3596,30 +3596,30 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3628,25 +3628,25 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3656,7 +3656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3717,24 +3717,24 @@
         <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920190</v>
+        <v>19330061430023</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -3745,16 +3745,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920195</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3765,39 +3765,39 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330061430023</v>
+        <v>21330051920197</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920195</v>
+        <v>21330051920198</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>56</v>
@@ -3805,16 +3805,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920195</v>
+        <v>21330051920198</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -3825,16 +3825,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920197</v>
+        <v>21330051920200</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -3845,56 +3845,56 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920198</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920198</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920198</v>
+        <v>21330051920207</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -3905,202 +3905,42 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920198</v>
+        <v>21330051920213</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920200</v>
+        <v>21330051920213</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920201</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920203</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920203</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920207</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920213</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920213</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920213</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920213</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4148,7 +3988,7 @@
         <v>88</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4165,89 +4005,89 @@
         <v>93</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920190</v>
+        <v>21330051920186</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920195</v>
+        <v>19330061430023</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920203</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920186</v>
+        <v>21330051920197</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4255,16 +4095,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920197</v>
+        <v>21330051920200</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4272,16 +4112,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920200</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4289,16 +4129,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920201</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4685,7 +4525,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4717,16 +4557,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920197</v>
+        <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4740,16 +4580,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920197</v>
+        <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4763,16 +4603,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920200</v>
+        <v>19330061430023</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4786,16 +4626,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920200</v>
+        <v>19330061430023</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4809,16 +4649,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920201</v>
+        <v>21330051920195</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4832,16 +4672,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920201</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4855,16 +4695,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920186</v>
+        <v>21330051920197</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4878,22 +4718,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920192</v>
+        <v>21330051920197</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4901,39 +4741,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920193</v>
+        <v>21330051920200</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920202</v>
+        <v>21330051920200</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4947,16 +4787,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920207</v>
+        <v>21330051920201</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4970,16 +4810,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920209</v>
+        <v>21330051920201</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -4988,6 +4828,144 @@
         <v>54</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920193</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920207</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920209</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20212.xlsx
+++ b/grupos/2BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -182,12 +182,12 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
@@ -212,253 +212,253 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>ELVIRA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>MEZA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>QUIJANO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROSALIANO</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
     <t>TZOPITL</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
   </si>
   <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>PEDRO EVER</t>
   </si>
   <si>
+    <t>NEIL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
+    <t>JULIO</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>CELSO ALEJANDRO</t>
+  </si>
+  <si>
     <t>PATRICIO</t>
   </si>
   <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
     <t>ADAHIR</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
     <t>ANGEL DANIEL</t>
   </si>
   <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>DIEGO HUMBERTO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
     <t>SINAI ANTONIO</t>
   </si>
   <si>
+    <t>ZURIEL ELIHU</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>ARIEL CHARBEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>ELVIRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>QUIJANO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROSALIANO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>ARIEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
   </si>
   <si>
     <t>DARINKA</t>
@@ -968,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -977,10 +977,10 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1016,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -1045,19 +1045,19 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1122,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1131,10 +1131,10 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1167,10 +1167,10 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1199,19 +1199,19 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1241,13 +1241,13 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1276,19 +1276,19 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1318,10 +1318,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1335,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1353,19 +1353,19 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1389,7 +1389,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1401,7 +1401,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1430,19 +1430,19 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1478,7 +1478,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1507,7 +1507,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1516,10 +1516,10 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1552,10 +1552,10 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1566,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1584,19 +1584,19 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1620,7 +1620,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1629,10 +1629,10 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1661,7 +1661,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1670,10 +1670,10 @@
         <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1709,7 +1709,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1720,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1738,19 +1738,19 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1774,19 +1774,19 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1815,7 +1815,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>9</v>
@@ -1824,10 +1824,10 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1874,7 +1874,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -1892,19 +1892,19 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1928,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1969,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -1978,10 +1978,10 @@
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2014,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2046,19 +2046,19 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2082,16 +2082,16 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2105,7 +2105,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2114,7 +2114,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2123,19 +2123,19 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2159,7 +2159,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2168,7 +2168,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2200,7 +2200,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2248,7 +2248,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2259,7 +2259,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2277,19 +2277,19 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2313,16 +2313,16 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>7</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2336,7 +2336,7 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2354,19 +2354,19 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2390,19 +2390,19 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>7</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2431,19 +2431,19 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2467,19 +2467,19 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2490,7 +2490,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -2508,19 +2508,19 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2544,7 +2544,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2553,10 +2553,10 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2585,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>9</v>
@@ -2594,10 +2594,10 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2662,7 +2662,7 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2671,10 +2671,10 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2710,7 +2710,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2721,7 +2721,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -2739,19 +2739,19 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>7</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2816,7 +2816,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>10</v>
@@ -2825,10 +2825,10 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2864,7 +2864,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2893,7 +2893,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>7</v>
@@ -2902,10 +2902,10 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2929,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2938,10 +2938,10 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2970,19 +2970,19 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3018,7 +3018,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3047,7 +3047,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -3056,10 +3056,10 @@
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3124,7 +3124,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>9</v>
@@ -3133,10 +3133,10 @@
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3160,7 +3160,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3172,7 +3172,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3201,19 +3201,19 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3243,13 +3243,13 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -3269,7 +3269,7 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -3278,19 +3278,19 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3314,7 +3314,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3323,10 +3323,10 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3355,7 +3355,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>7</v>
@@ -3364,10 +3364,10 @@
         <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3391,7 +3391,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3400,10 +3400,10 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3468,30 +3468,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>28.13</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3500,19 +3500,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>65.63</v>
+        <v>84.38</v>
       </c>
       <c r="G3">
-        <v>34.38</v>
+        <v>15.63</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3532,19 +3532,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3564,25 +3564,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>93.75</v>
+        <v>90.63</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3656,7 +3656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3681,266 +3681,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920186</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920190</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330061430023</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920195</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920197</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920198</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920198</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920200</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920201</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920203</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920207</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920213</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920213</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3976,200 +3716,200 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920198</v>
+        <v>21330051920185</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920213</v>
+        <v>21330051920186</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920186</v>
+        <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920190</v>
+        <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330061430023</v>
+        <v>21330051920189</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920195</v>
+        <v>21330051920190</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920197</v>
+        <v>21330051920191</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920200</v>
+        <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920201</v>
+        <v>21330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920203</v>
+        <v>19330061430023</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920207</v>
+        <v>21330051920194</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920185</v>
+        <v>21330051920195</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
         <v>127</v>
@@ -4180,13 +3920,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920187</v>
+        <v>21330051920196</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -4197,13 +3937,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920188</v>
+        <v>21330051920197</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>129</v>
@@ -4214,13 +3954,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920189</v>
+        <v>21330051920386</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>130</v>
@@ -4231,13 +3971,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920191</v>
+        <v>21330051920198</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
@@ -4248,10 +3988,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920192</v>
+        <v>21330051920199</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>104</v>
@@ -4265,13 +4005,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920193</v>
+        <v>21330051920200</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4282,13 +4022,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920194</v>
+        <v>21330051920201</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4299,13 +4039,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920196</v>
+        <v>21330051920202</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4316,13 +4056,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920386</v>
+        <v>21330051920203</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4333,13 +4073,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920199</v>
+        <v>21330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4350,13 +4090,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920202</v>
+        <v>21330051920205</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4367,13 +4107,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920204</v>
+        <v>21330051920206</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4384,13 +4124,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920205</v>
+        <v>21330051920207</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4401,13 +4141,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920206</v>
+        <v>21330051920208</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4418,13 +4158,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920208</v>
+        <v>21330051920209</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4435,13 +4175,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920209</v>
+        <v>21330051920210</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4452,13 +4192,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920210</v>
+        <v>21330051920211</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4469,13 +4209,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920211</v>
+        <v>21330051920212</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4486,13 +4226,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920212</v>
+        <v>21330051920213</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4506,10 +4246,10 @@
         <v>21330051920214</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4525,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4560,13 +4300,13 @@
         <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4575,7 +4315,7 @@
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4583,19 +4323,19 @@
         <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4603,16 +4343,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330061430023</v>
+        <v>21330051920197</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4621,24 +4361,24 @@
         <v>53</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920197</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
@@ -4649,16 +4389,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920195</v>
+        <v>21330051920200</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4667,27 +4407,27 @@
         <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920195</v>
+        <v>21330051920200</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4695,45 +4435,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920197</v>
+        <v>21330051920188</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920197</v>
+        <v>19330061430023</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4741,16 +4481,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920200</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4759,24 +4499,24 @@
         <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920200</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -4787,16 +4527,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920201</v>
+        <v>21330051920207</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4805,167 +4545,6 @@
         <v>53</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920201</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920186</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920192</v>
-      </c>
-      <c r="B15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920193</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920202</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920207</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920209</v>
-      </c>
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20212.xlsx
+++ b/grupos/2BEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -182,13 +182,13 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -983,28 +983,28 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>10</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1013,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1060,22 +1060,22 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1137,22 +1137,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1214,22 +1214,22 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1244,10 +1244,10 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1291,22 +1291,22 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1368,40 +1368,40 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>8</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1433,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -1445,22 +1445,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1522,28 +1522,28 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1552,10 +1552,10 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1599,37 +1599,37 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1676,28 +1676,28 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1709,7 +1709,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1753,28 +1753,28 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>10</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1786,7 +1786,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1830,28 +1830,28 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1907,28 +1907,28 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1937,10 +1937,10 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1984,22 +1984,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2061,22 +2061,22 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2088,13 +2088,13 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2138,25 +2138,25 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2165,7 +2165,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2215,22 +2215,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2292,22 +2292,22 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2319,10 +2319,10 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2369,28 +2369,28 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2399,10 +2399,10 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2446,28 +2446,28 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2476,10 +2476,10 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2523,22 +2523,22 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2550,7 +2550,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2600,22 +2600,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2677,22 +2677,22 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2754,28 +2754,28 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2831,28 +2831,28 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2908,22 +2908,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2938,7 +2938,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2985,34 +2985,34 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3062,28 +3062,28 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3092,7 +3092,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3139,28 +3139,28 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3216,28 +3216,28 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3246,10 +3246,10 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3293,37 +3293,37 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
         <v>8</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>7</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3370,28 +3370,28 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>9</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3468,19 +3468,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="G2">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3500,19 +3500,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>84.38</v>
+        <v>93.75</v>
       </c>
       <c r="G3">
-        <v>15.63</v>
+        <v>6.25</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3532,19 +3532,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>3.13</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3564,19 +3564,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4265,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4297,16 +4297,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920190</v>
+        <v>21330051920200</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4320,231 +4320,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920190</v>
+        <v>21330051920200</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920197</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920197</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920200</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920200</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920188</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330061430023</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920201</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920203</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920207</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20212.xlsx
+++ b/grupos/2BEM - Estadisticos 20212.xlsx
@@ -989,7 +989,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1143,7 +1143,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1220,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1238,7 +1238,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1297,7 +1297,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1315,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1374,7 +1374,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1451,7 +1451,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1528,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1546,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1605,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1623,7 +1623,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1682,7 +1682,7 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1700,7 +1700,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1759,7 +1759,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1836,7 +1836,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1913,7 +1913,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1931,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1990,7 +1990,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2067,7 +2067,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2162,7 +2162,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2221,7 +2221,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2298,7 +2298,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2316,7 +2316,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2375,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2393,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2452,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2470,7 +2470,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2529,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2606,7 +2606,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2624,7 +2624,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2683,7 +2683,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2760,7 +2760,7 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -2837,7 +2837,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2855,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2914,7 +2914,7 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2991,7 +2991,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3009,7 +3009,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3068,7 +3068,7 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3145,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3222,7 +3222,7 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -3299,7 +3299,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
